--- a/artfynd/A 27067-2024 artfynd.xlsx
+++ b/artfynd/A 27067-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,6 +782,349 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>118865667</v>
+      </c>
+      <c r="B3" t="n">
+        <v>90464</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>A 27067, Stormbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>579220</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6398579</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>118865729</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57443</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 27067, Stormbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>579436</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6398702</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>118865715</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57306</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 27067, Stormbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>579432</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6398712</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spår av födosök</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27067-2024 artfynd.xlsx
+++ b/artfynd/A 27067-2024 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118865667</v>
+        <v>118865715</v>
       </c>
       <c r="B3" t="n">
-        <v>90464</v>
+        <v>57306</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,34 +801,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5445</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -836,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579220</v>
+        <v>579432</v>
       </c>
       <c r="R3" t="n">
-        <v>6398579</v>
+        <v>6398712</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,13 +871,17 @@
           <t>2024-08-02</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spår av födosök</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118865729</v>
+        <v>118865667</v>
       </c>
       <c r="B4" t="n">
-        <v>57443</v>
+        <v>90464</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,35 +916,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5445</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579436</v>
+        <v>579220</v>
       </c>
       <c r="R4" t="n">
-        <v>6398702</v>
+        <v>6398579</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,6 +995,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1013,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118865715</v>
+        <v>118865729</v>
       </c>
       <c r="B5" t="n">
-        <v>57306</v>
+        <v>57443</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,29 +1030,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1061,13 +1066,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579432</v>
+        <v>579436</v>
       </c>
       <c r="R5" t="n">
-        <v>6398712</v>
+        <v>6398702</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1097,11 +1102,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-08-02</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Spår av födosök</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 27067-2024 artfynd.xlsx
+++ b/artfynd/A 27067-2024 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118865715</v>
+        <v>118865729</v>
       </c>
       <c r="B3" t="n">
-        <v>57306</v>
+        <v>57443</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,29 +801,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -833,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579432</v>
+        <v>579436</v>
       </c>
       <c r="R3" t="n">
-        <v>6398712</v>
+        <v>6398702</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,11 +873,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spår av födosök</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118865667</v>
+        <v>118865715</v>
       </c>
       <c r="B4" t="n">
-        <v>90464</v>
+        <v>57306</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,34 +915,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5445</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579220</v>
+        <v>579432</v>
       </c>
       <c r="R4" t="n">
-        <v>6398579</v>
+        <v>6398712</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,13 +985,17 @@
           <t>2024-08-02</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spår av födosök</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118865729</v>
+        <v>118865667</v>
       </c>
       <c r="B5" t="n">
-        <v>57443</v>
+        <v>90464</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,35 +1030,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>5445</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1066,13 +1065,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579436</v>
+        <v>579220</v>
       </c>
       <c r="R5" t="n">
-        <v>6398702</v>
+        <v>6398579</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,6 +1109,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 27067-2024 artfynd.xlsx
+++ b/artfynd/A 27067-2024 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118865729</v>
+        <v>118865667</v>
       </c>
       <c r="B3" t="n">
-        <v>57443</v>
+        <v>90471</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,35 +801,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>5445</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579436</v>
+        <v>579220</v>
       </c>
       <c r="R3" t="n">
-        <v>6398702</v>
+        <v>6398579</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,6 +880,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118865667</v>
+        <v>118865729</v>
       </c>
       <c r="B5" t="n">
-        <v>90464</v>
+        <v>57443</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,34 +1030,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5445</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1065,13 +1066,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579220</v>
+        <v>579436</v>
       </c>
       <c r="R5" t="n">
-        <v>6398579</v>
+        <v>6398702</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,7 +1110,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 27067-2024 artfynd.xlsx
+++ b/artfynd/A 27067-2024 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118865667</v>
+        <v>118865729</v>
       </c>
       <c r="B3" t="n">
-        <v>90471</v>
+        <v>57443</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,34 +801,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5445</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -836,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579220</v>
+        <v>579436</v>
       </c>
       <c r="R3" t="n">
-        <v>6398579</v>
+        <v>6398702</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +881,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118865729</v>
+        <v>118865667</v>
       </c>
       <c r="B5" t="n">
-        <v>57443</v>
+        <v>90471</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,35 +1030,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>5445</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1066,13 +1065,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579436</v>
+        <v>579220</v>
       </c>
       <c r="R5" t="n">
-        <v>6398702</v>
+        <v>6398579</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,6 +1109,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 27067-2024 artfynd.xlsx
+++ b/artfynd/A 27067-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118281573</v>
+        <v>118847474</v>
       </c>
       <c r="B2" t="n">
-        <v>57306</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,31 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5445</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579230</v>
+        <v>579164</v>
       </c>
       <c r="R2" t="n">
-        <v>6398644</v>
+        <v>6398564</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,12 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,6 +765,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118865667</v>
+        <v>118847543</v>
       </c>
       <c r="B3" t="n">
-        <v>90473</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,7 +814,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -836,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579220</v>
+        <v>579181</v>
       </c>
       <c r="R3" t="n">
-        <v>6398579</v>
+        <v>6398551</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118865729</v>
+        <v>118865667</v>
       </c>
       <c r="B4" t="n">
-        <v>57445</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,35 +904,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5445</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579436</v>
+        <v>579220</v>
       </c>
       <c r="R4" t="n">
-        <v>6398702</v>
+        <v>6398579</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,6 +983,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1013,15 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118865715</v>
+        <v>118865677</v>
       </c>
       <c r="B5" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1029,31 +1013,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5445</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1061,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579432</v>
+        <v>579225</v>
       </c>
       <c r="R5" t="n">
-        <v>6398712</v>
+        <v>6398552</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,17 +1086,13 @@
           <t>2024-08-02</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Spår av födosök</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1125,6 +1108,1078 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>118865749</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91867</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 27067, Stormbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>579228</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6398560</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>118865796</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91867</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 27067, Stormbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>579224</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6398565</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>118281573</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 27067, Stormbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>579230</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6398644</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>118865652</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 27067, Stormbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>579059</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6398651</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Spår av födosök</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>118865715</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 27067, Stormbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>579432</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6398712</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Spår av födosök</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>119180160</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58067</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100090</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Nötkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nucifraga caryocatactes</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 27067, Stormbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>579278</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6398844</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-08-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-08-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131740413</v>
+      </c>
+      <c r="B12" t="n">
+        <v>4989</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100307</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blompraktbagge</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Anthaxia morio</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1792)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ugglekärr Nordost, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>579462</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6398836</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>118865729</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>A 27067, Stormbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>579436</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6398702</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>119624097</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>A 27067, Stormbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>579120</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6398550</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131740065</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ugglekärr Nordost, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>579462</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6398659</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Lynx Beverskog</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
